--- a/artfynd/A 18655-2025 artfynd.xlsx
+++ b/artfynd/A 18655-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69370168</v>
+        <v>136636515</v>
       </c>
       <c r="B2" t="n">
-        <v>56827</v>
+        <v>92373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,56 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100087</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fransfladdermus</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Myotis nattereri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Spelåen, Ång</t>
+          <t>Sprängsviken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>645510</v>
+        <v>645811</v>
       </c>
       <c r="R2" t="n">
-        <v>6972854</v>
+        <v>6973115</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-07-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-07-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,93 +771,69 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Björksnår</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69370168</t>
+          <t>https://artportalen.se/Sighting/136636515</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>69370543</v>
+        <v>136636517</v>
       </c>
       <c r="B3" t="n">
-        <v>56823</v>
+        <v>92373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205992</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Spelåen, Ång</t>
+          <t>Sprängsviken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>645510</v>
+        <v>645822</v>
       </c>
       <c r="R3" t="n">
-        <v>6972854</v>
+        <v>6973120</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -900,22 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-07-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-07-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,36 +883,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Björksnår</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69370543</t>
+          <t>https://artportalen.se/Sighting/136636517</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>69371119</v>
+        <v>136636518</v>
       </c>
       <c r="B4" t="n">
-        <v>56816</v>
+        <v>92373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,56 +915,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spelåen, Ång</t>
+          <t>Sprängsviken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>645510</v>
+        <v>645814</v>
       </c>
       <c r="R4" t="n">
-        <v>6972854</v>
+        <v>6973130</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1036,22 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-07-27</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-07-28</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1062,27 +995,2728 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Björksnår</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Martin Brüsin</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136636518</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136636522</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92373</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>658</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sprängsviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>645799</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6973202</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636522</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136636523</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92373</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>658</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sprängsviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>645795</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6973210</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636523</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136636526</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92373</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>658</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sprängsviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>645767</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6973132</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636526</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136636529</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92373</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>658</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sprängsviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>645641</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6972927</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636529</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136636509</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92102</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sprängsviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>645904</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6973066</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636509</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136636519</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92102</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sprängsviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>645802</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6973139</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636519</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136636527</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92102</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sprängsviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>645805</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6973118</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636527</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136636511</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92116</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sprängsviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>645884</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6973054</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636511</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136636507</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92534</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sprängsviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>645909</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6973065</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636507</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136636520</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92534</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sprängsviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>645802</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6973139</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636520</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136636508</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92065</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sprängsviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>645905</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6973069</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636508</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136636512</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92065</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sprängsviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>645847</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6973126</v>
+      </c>
+      <c r="S16" t="n">
+        <v>12</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636512</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136636524</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92065</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sprängsviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>645814</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6973241</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636524</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136636525</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92065</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sprängsviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>645807</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6973232</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636525</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>69370168</v>
+      </c>
+      <c r="B19" t="n">
+        <v>56827</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100087</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fransfladdermus</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Myotis nattereri</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Spelåen, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>645510</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6972854</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2017-07-27</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2017-07-28</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Björksnår</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69370168</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136636516</v>
+      </c>
+      <c r="B20" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sprängsviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>645831</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6973128</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636516</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136636528</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sprängsviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>645803</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6973110</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636528</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136636506</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57998</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100110</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Gråspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picus canus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sprängsviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>645979</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6973048</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636506</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136636510</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sprängsviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>645890</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6973062</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636510</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136636521</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58162</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sprängsviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>645809</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6973193</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636521</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>69370543</v>
+      </c>
+      <c r="B25" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Spelåen, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>645510</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6972854</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2017-07-27</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2017-07-28</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Björksnår</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69370543</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>69371119</v>
+      </c>
+      <c r="B26" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Spelåen, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>645510</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6972854</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2017-07-27</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2017-07-28</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Björksnår</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/69371119</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136636514</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79497</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sprängsviken, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>645820</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6973114</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Kramfors</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:43</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136636514</t>
         </is>
       </c>
     </row>
@@ -1091,6 +3725,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 18655-2025 artfynd.xlsx
+++ b/artfynd/A 18655-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136636515</v>
       </c>
       <c r="B2" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136636517</v>
       </c>
       <c r="B3" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136636518</v>
       </c>
       <c r="B4" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136636522</v>
       </c>
       <c r="B5" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136636523</v>
       </c>
       <c r="B6" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136636526</v>
       </c>
       <c r="B7" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136636529</v>
       </c>
       <c r="B8" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136636509</v>
       </c>
       <c r="B9" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136636519</v>
       </c>
       <c r="B10" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136636527</v>
       </c>
       <c r="B11" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136636511</v>
       </c>
       <c r="B12" t="n">
-        <v>92116</v>
+        <v>92119</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136636507</v>
       </c>
       <c r="B13" t="n">
-        <v>92534</v>
+        <v>92537</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136636520</v>
       </c>
       <c r="B14" t="n">
-        <v>92534</v>
+        <v>92537</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136636508</v>
       </c>
       <c r="B15" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136636512</v>
       </c>
       <c r="B16" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136636524</v>
       </c>
       <c r="B17" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136636525</v>
       </c>
       <c r="B18" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 18655-2025 artfynd.xlsx
+++ b/artfynd/A 18655-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136636515</v>
       </c>
       <c r="B2" t="n">
-        <v>92376</v>
+        <v>92377</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136636517</v>
       </c>
       <c r="B3" t="n">
-        <v>92376</v>
+        <v>92377</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136636518</v>
       </c>
       <c r="B4" t="n">
-        <v>92376</v>
+        <v>92377</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136636522</v>
       </c>
       <c r="B5" t="n">
-        <v>92376</v>
+        <v>92377</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136636523</v>
       </c>
       <c r="B6" t="n">
-        <v>92376</v>
+        <v>92377</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136636526</v>
       </c>
       <c r="B7" t="n">
-        <v>92376</v>
+        <v>92377</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136636529</v>
       </c>
       <c r="B8" t="n">
-        <v>92376</v>
+        <v>92377</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136636509</v>
       </c>
       <c r="B9" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136636519</v>
       </c>
       <c r="B10" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136636527</v>
       </c>
       <c r="B11" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136636511</v>
       </c>
       <c r="B12" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136636507</v>
       </c>
       <c r="B13" t="n">
-        <v>92537</v>
+        <v>92538</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136636520</v>
       </c>
       <c r="B14" t="n">
-        <v>92537</v>
+        <v>92538</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136636508</v>
       </c>
       <c r="B15" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136636512</v>
       </c>
       <c r="B16" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136636524</v>
       </c>
       <c r="B17" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136636525</v>
       </c>
       <c r="B18" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 18655-2025 artfynd.xlsx
+++ b/artfynd/A 18655-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136636515</v>
       </c>
       <c r="B2" t="n">
-        <v>92377</v>
+        <v>92382</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136636517</v>
       </c>
       <c r="B3" t="n">
-        <v>92377</v>
+        <v>92382</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136636518</v>
       </c>
       <c r="B4" t="n">
-        <v>92377</v>
+        <v>92382</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136636522</v>
       </c>
       <c r="B5" t="n">
-        <v>92377</v>
+        <v>92382</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136636523</v>
       </c>
       <c r="B6" t="n">
-        <v>92377</v>
+        <v>92382</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136636526</v>
       </c>
       <c r="B7" t="n">
-        <v>92377</v>
+        <v>92382</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136636529</v>
       </c>
       <c r="B8" t="n">
-        <v>92377</v>
+        <v>92382</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136636509</v>
       </c>
       <c r="B9" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136636519</v>
       </c>
       <c r="B10" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136636527</v>
       </c>
       <c r="B11" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136636511</v>
       </c>
       <c r="B12" t="n">
-        <v>92120</v>
+        <v>92125</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136636507</v>
       </c>
       <c r="B13" t="n">
-        <v>92538</v>
+        <v>92543</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136636520</v>
       </c>
       <c r="B14" t="n">
-        <v>92538</v>
+        <v>92543</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136636508</v>
       </c>
       <c r="B15" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136636512</v>
       </c>
       <c r="B16" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136636524</v>
       </c>
       <c r="B17" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136636525</v>
       </c>
       <c r="B18" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136636516</v>
       </c>
       <c r="B20" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>136636528</v>
       </c>
       <c r="B21" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>136636506</v>
       </c>
       <c r="B22" t="n">
-        <v>57998</v>
+        <v>58000</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>136636510</v>
       </c>
       <c r="B23" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>136636521</v>
       </c>
       <c r="B24" t="n">
-        <v>58162</v>
+        <v>58164</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>136636514</v>
       </c>
       <c r="B27" t="n">
-        <v>79497</v>
+        <v>79499</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 18655-2025 artfynd.xlsx
+++ b/artfynd/A 18655-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136636515</v>
       </c>
       <c r="B2" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136636517</v>
       </c>
       <c r="B3" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136636518</v>
       </c>
       <c r="B4" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136636522</v>
       </c>
       <c r="B5" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136636523</v>
       </c>
       <c r="B6" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136636526</v>
       </c>
       <c r="B7" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136636529</v>
       </c>
       <c r="B8" t="n">
-        <v>92382</v>
+        <v>92384</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136636509</v>
       </c>
       <c r="B9" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136636519</v>
       </c>
       <c r="B10" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136636527</v>
       </c>
       <c r="B11" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136636511</v>
       </c>
       <c r="B12" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136636507</v>
       </c>
       <c r="B13" t="n">
-        <v>92543</v>
+        <v>92545</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136636520</v>
       </c>
       <c r="B14" t="n">
-        <v>92543</v>
+        <v>92545</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136636508</v>
       </c>
       <c r="B15" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136636512</v>
       </c>
       <c r="B16" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136636524</v>
       </c>
       <c r="B17" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136636525</v>
       </c>
       <c r="B18" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 18655-2025 artfynd.xlsx
+++ b/artfynd/A 18655-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136636515</v>
       </c>
       <c r="B2" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136636517</v>
       </c>
       <c r="B3" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136636518</v>
       </c>
       <c r="B4" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136636522</v>
       </c>
       <c r="B5" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136636523</v>
       </c>
       <c r="B6" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136636526</v>
       </c>
       <c r="B7" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136636529</v>
       </c>
       <c r="B8" t="n">
-        <v>92384</v>
+        <v>92386</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136636509</v>
       </c>
       <c r="B9" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136636519</v>
       </c>
       <c r="B10" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136636527</v>
       </c>
       <c r="B11" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136636511</v>
       </c>
       <c r="B12" t="n">
-        <v>92127</v>
+        <v>92129</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136636507</v>
       </c>
       <c r="B13" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136636520</v>
       </c>
       <c r="B14" t="n">
-        <v>92545</v>
+        <v>92547</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136636508</v>
       </c>
       <c r="B15" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136636512</v>
       </c>
       <c r="B16" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136636524</v>
       </c>
       <c r="B17" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136636525</v>
       </c>
       <c r="B18" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>136636514</v>
       </c>
       <c r="B27" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 18655-2025 artfynd.xlsx
+++ b/artfynd/A 18655-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136636515</v>
       </c>
       <c r="B2" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136636517</v>
       </c>
       <c r="B3" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136636518</v>
       </c>
       <c r="B4" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136636522</v>
       </c>
       <c r="B5" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136636523</v>
       </c>
       <c r="B6" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136636526</v>
       </c>
       <c r="B7" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136636529</v>
       </c>
       <c r="B8" t="n">
-        <v>92386</v>
+        <v>92388</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136636509</v>
       </c>
       <c r="B9" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136636519</v>
       </c>
       <c r="B10" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136636527</v>
       </c>
       <c r="B11" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136636511</v>
       </c>
       <c r="B12" t="n">
-        <v>92129</v>
+        <v>92131</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136636507</v>
       </c>
       <c r="B13" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136636520</v>
       </c>
       <c r="B14" t="n">
-        <v>92547</v>
+        <v>92549</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136636508</v>
       </c>
       <c r="B15" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136636512</v>
       </c>
       <c r="B16" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136636524</v>
       </c>
       <c r="B17" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136636525</v>
       </c>
       <c r="B18" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>136636514</v>
       </c>
       <c r="B27" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 18655-2025 artfynd.xlsx
+++ b/artfynd/A 18655-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136636515</v>
       </c>
       <c r="B2" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136636517</v>
       </c>
       <c r="B3" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136636518</v>
       </c>
       <c r="B4" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136636522</v>
       </c>
       <c r="B5" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136636523</v>
       </c>
       <c r="B6" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136636526</v>
       </c>
       <c r="B7" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136636529</v>
       </c>
       <c r="B8" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136636509</v>
       </c>
       <c r="B9" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136636519</v>
       </c>
       <c r="B10" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136636527</v>
       </c>
       <c r="B11" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136636511</v>
       </c>
       <c r="B12" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136636507</v>
       </c>
       <c r="B13" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136636520</v>
       </c>
       <c r="B14" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136636508</v>
       </c>
       <c r="B15" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136636512</v>
       </c>
       <c r="B16" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136636524</v>
       </c>
       <c r="B17" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136636525</v>
       </c>
       <c r="B18" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>136636514</v>
       </c>
       <c r="B27" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 18655-2025 artfynd.xlsx
+++ b/artfynd/A 18655-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136636515</v>
       </c>
       <c r="B2" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136636517</v>
       </c>
       <c r="B3" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136636518</v>
       </c>
       <c r="B4" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136636522</v>
       </c>
       <c r="B5" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136636523</v>
       </c>
       <c r="B6" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136636526</v>
       </c>
       <c r="B7" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136636529</v>
       </c>
       <c r="B8" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136636509</v>
       </c>
       <c r="B9" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136636519</v>
       </c>
       <c r="B10" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136636527</v>
       </c>
       <c r="B11" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136636511</v>
       </c>
       <c r="B12" t="n">
-        <v>92132</v>
+        <v>92138</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136636507</v>
       </c>
       <c r="B13" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136636520</v>
       </c>
       <c r="B14" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136636508</v>
       </c>
       <c r="B15" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136636512</v>
       </c>
       <c r="B16" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136636524</v>
       </c>
       <c r="B17" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136636525</v>
       </c>
       <c r="B18" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 18655-2025 artfynd.xlsx
+++ b/artfynd/A 18655-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136636515</v>
       </c>
       <c r="B2" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136636517</v>
       </c>
       <c r="B3" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136636518</v>
       </c>
       <c r="B4" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136636522</v>
       </c>
       <c r="B5" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136636523</v>
       </c>
       <c r="B6" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136636526</v>
       </c>
       <c r="B7" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136636529</v>
       </c>
       <c r="B8" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136636509</v>
       </c>
       <c r="B9" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136636519</v>
       </c>
       <c r="B10" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136636527</v>
       </c>
       <c r="B11" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136636511</v>
       </c>
       <c r="B12" t="n">
-        <v>92138</v>
+        <v>92142</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136636507</v>
       </c>
       <c r="B13" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136636520</v>
       </c>
       <c r="B14" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136636508</v>
       </c>
       <c r="B15" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136636512</v>
       </c>
       <c r="B16" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136636524</v>
       </c>
       <c r="B17" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136636525</v>
       </c>
       <c r="B18" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>136636514</v>
       </c>
       <c r="B27" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 18655-2025 artfynd.xlsx
+++ b/artfynd/A 18655-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136636515</v>
       </c>
       <c r="B2" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136636517</v>
       </c>
       <c r="B3" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136636518</v>
       </c>
       <c r="B4" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136636522</v>
       </c>
       <c r="B5" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136636523</v>
       </c>
       <c r="B6" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136636526</v>
       </c>
       <c r="B7" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136636529</v>
       </c>
       <c r="B8" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136636509</v>
       </c>
       <c r="B9" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136636519</v>
       </c>
       <c r="B10" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136636527</v>
       </c>
       <c r="B11" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136636511</v>
       </c>
       <c r="B12" t="n">
-        <v>92142</v>
+        <v>92144</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136636507</v>
       </c>
       <c r="B13" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136636520</v>
       </c>
       <c r="B14" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136636508</v>
       </c>
       <c r="B15" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136636512</v>
       </c>
       <c r="B16" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136636524</v>
       </c>
       <c r="B17" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136636525</v>
       </c>
       <c r="B18" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>136636514</v>
       </c>
       <c r="B27" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 18655-2025 artfynd.xlsx
+++ b/artfynd/A 18655-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136636515</v>
       </c>
       <c r="B2" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136636517</v>
       </c>
       <c r="B3" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136636518</v>
       </c>
       <c r="B4" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136636522</v>
       </c>
       <c r="B5" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136636523</v>
       </c>
       <c r="B6" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136636526</v>
       </c>
       <c r="B7" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136636529</v>
       </c>
       <c r="B8" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136636509</v>
       </c>
       <c r="B9" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136636519</v>
       </c>
       <c r="B10" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136636527</v>
       </c>
       <c r="B11" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136636511</v>
       </c>
       <c r="B12" t="n">
-        <v>92144</v>
+        <v>92157</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136636507</v>
       </c>
       <c r="B13" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136636520</v>
       </c>
       <c r="B14" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136636508</v>
       </c>
       <c r="B15" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136636512</v>
       </c>
       <c r="B16" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136636524</v>
       </c>
       <c r="B17" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136636525</v>
       </c>
       <c r="B18" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136636516</v>
       </c>
       <c r="B20" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>136636528</v>
       </c>
       <c r="B21" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>136636506</v>
       </c>
       <c r="B22" t="n">
-        <v>58000</v>
+        <v>58013</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>136636510</v>
       </c>
       <c r="B23" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>136636521</v>
       </c>
       <c r="B24" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>136636514</v>
       </c>
       <c r="B27" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 18655-2025 artfynd.xlsx
+++ b/artfynd/A 18655-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136636515</v>
       </c>
       <c r="B2" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136636517</v>
       </c>
       <c r="B3" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136636518</v>
       </c>
       <c r="B4" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136636522</v>
       </c>
       <c r="B5" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136636523</v>
       </c>
       <c r="B6" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136636526</v>
       </c>
       <c r="B7" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>136636529</v>
       </c>
       <c r="B8" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>136636509</v>
       </c>
       <c r="B9" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>136636519</v>
       </c>
       <c r="B10" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>136636527</v>
       </c>
       <c r="B11" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>136636511</v>
       </c>
       <c r="B12" t="n">
-        <v>92157</v>
+        <v>92159</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>136636507</v>
       </c>
       <c r="B13" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>136636520</v>
       </c>
       <c r="B14" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>136636508</v>
       </c>
       <c r="B15" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>136636512</v>
       </c>
       <c r="B16" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>136636524</v>
       </c>
       <c r="B17" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>136636525</v>
       </c>
       <c r="B18" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>136636516</v>
       </c>
       <c r="B20" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>136636528</v>
       </c>
       <c r="B21" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2973,7 +2973,7 @@
         <v>136636506</v>
       </c>
       <c r="B22" t="n">
-        <v>58013</v>
+        <v>58015</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>136636510</v>
       </c>
       <c r="B23" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>136636521</v>
       </c>
       <c r="B24" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         <v>136636514</v>
       </c>
       <c r="B27" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
